--- a/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.2.非同期処理方式.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.2.非同期処理方式.xlsx
@@ -1,23 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E98E98-3B6A-41CB-8BB4-3540418929AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A2068E-5E91-4662-B619-0CC6B3EB1077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.2.非同期処理方式" sheetId="13" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3.2.非同期処理方式'!$J$18:$Q$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.2.非同期処理方式'!$A$1:$AI$45</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'3.2.非同期処理方式'!$A$1:$AI$45</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'3.2.非同期処理方式'!$A$1:$AI$45</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'3.2.非同期処理方式'!$A$1:$AI$45</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'3.2.非同期処理方式'!$A$1:$AI$45</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1248,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI476"/>
